--- a/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -431,7 +431,7 @@
   <x:dimension ref="A1:A16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38.567768" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">

--- a/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -490,18 +490,21 @@
       </x:c>
     </x:row>
     <x:row r="12" spans="1:1">
-      <x:c r="A12" s="0">
+      <x:c r="A12" s="0" t="str">
         <x:f>HYPERLINK("mailto:test@test.com", "Send Email through formula")</x:f>
+        <x:v>Send Email through formula</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:1">
-      <x:c r="A13" s="0">
+      <x:c r="A13" s="0" t="str">
         <x:f>HYPERLINK("[Hyperlinks.xlsx]Hyperlinks!B2:C4", "Link to range through formula")</x:f>
+        <x:v>Link to range through formula</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:1">
-      <x:c r="A14" s="0">
+      <x:c r="A14" s="0" t="str">
         <x:f>HYPERLINK("[../Test.xlsx]Sheet1!B2:C4", "Link to another file through formula")</x:f>
+        <x:v>Link to another file through formula</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
